--- a/Collections/Ukraine/#Ukraine#Commercial#[2004-present]#circulation_quality.xlsx
+++ b/Collections/Ukraine/#Ukraine#Commercial#[2004-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Ukraine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21709AD8-A960-4D45-AE2C-DECD0D165157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5205E3-D910-4F3D-80A3-02B3D2EF5BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="33150" windowHeight="17700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" 1гривня" sheetId="10" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="52">
   <si>
     <t>-</t>
   </si>
@@ -193,9 +193,6 @@
     <t>10гривень</t>
   </si>
   <si>
-    <t>5 000 000</t>
-  </si>
-  <si>
     <t>60 Years of Liberation of Ukraine from Fascist Invaders</t>
   </si>
   <si>
@@ -211,15 +208,9 @@
     <t>70th Anniversary of the End of World War II in Europe</t>
   </si>
   <si>
-    <t>7 000 000</t>
-  </si>
-  <si>
     <t>20 Years of Monetary Reform in Ukraine</t>
   </si>
   <si>
-    <t>60 000</t>
-  </si>
-  <si>
     <t>Territorial Defense Forces of Armed Forces of Ukraine</t>
   </si>
   <si>
@@ -257,13 +248,49 @@
   </si>
   <si>
     <t>National Guard of Ukraine</t>
+  </si>
+  <si>
+    <t>Subtype_2#Composition</t>
+  </si>
+  <si>
+    <t>Subtype_1#Series</t>
+  </si>
+  <si>
+    <t>We are strong. We are together</t>
+  </si>
+  <si>
+    <t>Luhansk Oblast</t>
+  </si>
+  <si>
+    <t>Donetsk Oblast</t>
+  </si>
+  <si>
+    <t>Autonomous Republic of Crimea</t>
+  </si>
+  <si>
+    <t>Unmanned Systems Forces of the Armed Forces of Ukraine</t>
+  </si>
+  <si>
+    <t>2.000.000</t>
+  </si>
+  <si>
+    <t>10.000.000</t>
+  </si>
+  <si>
+    <t>5.000.000</t>
+  </si>
+  <si>
+    <t>7.000.000</t>
+  </si>
+  <si>
+    <t>60.000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -326,6 +353,10 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -503,7 +534,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -597,6 +628,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -605,9 +642,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -616,7 +650,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -624,23 +658,6 @@
           <bgColor rgb="FF9BE5FF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -770,6 +787,55 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -791,9 +857,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="23" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1108,14 +1174,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="27"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="25" t="s">
         <v>3</v>
       </c>
@@ -1124,15 +1190,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>4</v>
@@ -1146,14 +1212,14 @@
         <v>2004</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -1168,14 +1234,14 @@
         <v>2005</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F4" s="8">
         <v>0</v>
@@ -1286,16 +1352,16 @@
         <v>2010</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="37">
+        <v>49</v>
+      </c>
+      <c r="F9" s="34">
         <v>1</v>
       </c>
       <c r="G9" s="30" t="str">
@@ -1332,14 +1398,14 @@
         <v>2012</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -1426,12 +1492,12 @@
         <v>2015</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -1446,12 +1512,12 @@
         <v>2016</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="22" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>0</v>
@@ -1756,12 +1822,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15 F3:F4">
-    <cfRule type="containsText" dxfId="20" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9 F11">
-    <cfRule type="containsText" dxfId="19" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1790,12 +1856,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="18" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17:F27">
-    <cfRule type="containsText" dxfId="17" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1812,7 +1878,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="16" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1829,7 +1895,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="15" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1846,7 +1912,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="14" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1863,7 +1929,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1880,7 +1946,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1897,7 +1963,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1914,7 +1980,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1931,7 +1997,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1943,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C985906-1F40-4F9F-A28B-610F2E45FBC5}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -1955,14 +2021,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="27"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="21" t="s">
         <v>3</v>
       </c>
@@ -1973,12 +2039,12 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>40</v>
@@ -2503,14 +2569,14 @@
         <v>2022</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="23">
-        <v>10000000</v>
+      <c r="E24" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F24" s="8">
         <v>0</v>
@@ -2525,14 +2591,14 @@
         <v>2023</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="23">
-        <v>10000000</v>
+      <c r="E25" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -2547,20 +2613,20 @@
         <v>2023</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="23">
-        <v>10000000</v>
+      <c r="E26" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F26" s="8">
         <v>0</v>
       </c>
       <c r="G26" s="15" t="str">
-        <f t="shared" ref="G26:G32" si="3">IF(OR(AND(F26&gt;1,F26&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G26:G33" si="3">IF(OR(AND(F26&gt;1,F26&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2569,14 +2635,14 @@
         <v>2023</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="23">
-        <v>10000000</v>
+      <c r="E27" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F27" s="8">
         <v>0</v>
@@ -2591,14 +2657,14 @@
         <v>2023</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="23">
-        <v>10000000</v>
+      <c r="E28" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F28" s="8">
         <v>0</v>
@@ -2613,14 +2679,14 @@
         <v>2024</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="23">
-        <v>10000000</v>
+      <c r="E29" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F29" s="8">
         <v>0</v>
@@ -2635,14 +2701,14 @@
         <v>2024</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="23">
-        <v>10000000</v>
+      <c r="E30" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F30" s="8">
         <v>0</v>
@@ -2657,14 +2723,14 @@
         <v>2024</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="23">
-        <v>10000000</v>
+      <c r="E31" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F31" s="8">
         <v>0</v>
@@ -2679,14 +2745,14 @@
         <v>2024</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="23">
-        <v>10000000</v>
+      <c r="E32" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F32" s="8">
         <v>0</v>
@@ -2697,24 +2763,24 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="32">
+      <c r="A33" s="33">
         <v>2025</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="23">
-        <v>10000000</v>
+      <c r="E33" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="F33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="15" t="str">
-        <f t="shared" ref="G33:G34" si="4">IF(OR(AND(F33&gt;1,F33&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2723,31 +2789,125 @@
         <v>2025</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="8">
+        <v>1</v>
+      </c>
+      <c r="G34" s="15" t="str">
+        <f t="shared" ref="G34:G35" si="4">IF(OR(AND(F34&gt;1,F34&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="33">
+        <v>2025</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="23">
-        <v>10000000</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0</v>
-      </c>
-      <c r="G34" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G50" s="15" t="str">
-        <f>IF(OR(AND(F29&gt;1,F29&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="E36" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0</v>
+      </c>
+      <c r="G36" s="15" t="str">
+        <f t="shared" ref="G36:G38" si="5">IF(OR(AND(F36&gt;1,F36&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="33">
+        <v>2025</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="33">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="8">
+        <v>0</v>
+      </c>
+      <c r="G38" s="15" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G51" s="15" t="str">
+        <f>IF(OR(AND(F29&gt;1,F29&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G52" s="15" t="str">
         <f>IF(OR(AND(F30&gt;1,F30&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
@@ -2758,8 +2918,9 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2771,11 +2932,79 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="8" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25 F27 F29 F31">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25 F27 F29 F31">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26 F28 F30 F32">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26 F28 F30 F32">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2787,12 +3016,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25 F27 F29 F31">
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26 F28 F30 F32">
+  <conditionalFormatting sqref="F36">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2804,12 +3033,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26 F28 F30 F32">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F36">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
+  <conditionalFormatting sqref="F37">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2821,12 +3050,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F37">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2838,12 +3067,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F38">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F33">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2855,7 +3084,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F33">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>

--- a/Collections/Ukraine/#Ukraine#Commercial#[2004-present]#circulation_quality.xlsx
+++ b/Collections/Ukraine/#Ukraine#Commercial#[2004-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Ukraine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5205E3-D910-4F3D-80A3-02B3D2EF5BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF418987-99CF-4E15-B62D-E0AFF104B1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" 1гривня" sheetId="10" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="52">
   <si>
     <t>-</t>
   </si>
@@ -357,6 +357,8 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="9">
@@ -409,7 +411,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -528,13 +530,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -642,6 +659,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +673,48 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -827,15 +891,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -857,9 +912,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="23" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="5" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1408,7 +1463,7 @@
         <v>49</v>
       </c>
       <c r="F11" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="30" t="str">
         <f t="shared" si="0"/>
@@ -1487,7 +1542,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>2015</v>
       </c>
@@ -1499,8 +1554,8 @@
       <c r="E15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="8">
-        <v>0</v>
+      <c r="F15" s="40">
+        <v>1</v>
       </c>
       <c r="G15" s="30" t="str">
         <f t="shared" si="0"/>
@@ -1519,7 +1574,7 @@
       <c r="E16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="39">
         <v>0</v>
       </c>
       <c r="G16" s="30" t="str">
@@ -1798,6 +1853,18 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F4 F15">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11 F9">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1809,8 +1876,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F15 F3:F4">
+    <cfRule type="containsText" dxfId="28" priority="109" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F9 F11">
-    <cfRule type="colorScale" priority="106">
+    <cfRule type="containsText" dxfId="27" priority="107" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F27">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1821,18 +1898,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15 F3:F4">
-    <cfRule type="containsText" dxfId="21" priority="107" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9 F11">
-    <cfRule type="containsText" dxfId="20" priority="105" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F27">
-    <cfRule type="colorScale" priority="54">
+  <conditionalFormatting sqref="F8">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1844,7 +1911,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="containsText" dxfId="26" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F27">
+    <cfRule type="containsText" dxfId="25" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1855,18 +1932,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="19" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F27">
-    <cfRule type="containsText" dxfId="18" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="containsText" dxfId="24" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1877,12 +1949,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="23" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1894,12 +1966,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1911,12 +1983,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="15" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1928,12 +2000,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1945,12 +2017,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F13">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1962,25 +2034,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1997,8 +2052,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2630,7 +2685,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="26">
         <v>2023</v>
       </c>
@@ -2644,7 +2699,7 @@
       <c r="E27" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="40">
         <v>0</v>
       </c>
       <c r="G27" s="15" t="str">
@@ -2740,7 +2795,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="26">
         <v>2024</v>
       </c>
@@ -2754,7 +2809,7 @@
       <c r="E32" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="40">
         <v>0</v>
       </c>
       <c r="G32" s="15" t="str">
@@ -2852,7 +2907,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="33">
         <v>2025</v>
       </c>
@@ -2868,7 +2923,7 @@
       <c r="E37" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="40">
         <v>0</v>
       </c>
       <c r="G37" s="15" t="str">
@@ -2920,7 +2975,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2932,11 +2987,62 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="9" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25 F27 F29 F31">
+  <conditionalFormatting sqref="F25 F29 F31">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25 F29 F31">
+    <cfRule type="containsText" dxfId="15" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26 F28 F30">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26 F28 F30">
+    <cfRule type="containsText" dxfId="14" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="13" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2948,12 +3054,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25 F27 F29 F31">
-    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26 F28 F30 F32">
+  <conditionalFormatting sqref="F35">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2965,12 +3071,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26 F28 F30 F32">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
+  <conditionalFormatting sqref="F36">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2982,29 +3088,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F36">
+    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
+  <conditionalFormatting sqref="F38">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3016,12 +3105,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F38">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
+  <conditionalFormatting sqref="F33">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3033,12 +3122,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3050,12 +3139,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F27">
     <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
+  <conditionalFormatting sqref="F32">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3067,12 +3156,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
+  <conditionalFormatting sqref="F32">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F37">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3084,7 +3173,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F37">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
